--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-24.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
   <si>
     <t>Date: 2024-11-24</t>
   </si>
@@ -68,16 +68,16 @@
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
   </si>
   <si>
     <t>58</t>
@@ -89,79 +89,79 @@
     <t>45</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>1,102,042,261.3</t>
-  </si>
-  <si>
-    <t>732,548,899.9</t>
-  </si>
-  <si>
-    <t>612,915,084.88</t>
-  </si>
-  <si>
-    <t>500,197,672.15</t>
-  </si>
-  <si>
-    <t>483,429,819.6</t>
-  </si>
-  <si>
-    <t>455,144,537.8</t>
-  </si>
-  <si>
-    <t>446,331,342.7</t>
-  </si>
-  <si>
-    <t>531,470,001.0</t>
-  </si>
-  <si>
-    <t>422,569,002.8</t>
-  </si>
-  <si>
-    <t>345,882,321.08</t>
-  </si>
-  <si>
-    <t>225,556,887.7</t>
-  </si>
-  <si>
-    <t>219,891,575.6</t>
-  </si>
-  <si>
-    <t>177,872,430.3</t>
-  </si>
-  <si>
-    <t>184,429,783.1</t>
-  </si>
-  <si>
-    <t>570,572,260.29</t>
-  </si>
-  <si>
-    <t>309,979,897.1</t>
-  </si>
-  <si>
-    <t>267,032,763.8</t>
-  </si>
-  <si>
-    <t>274,640,784.45</t>
-  </si>
-  <si>
-    <t>263,538,244.0</t>
-  </si>
-  <si>
-    <t>277,272,107.5</t>
-  </si>
-  <si>
-    <t>261,901,559.6</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>1,088,465,241.69</t>
+  </si>
+  <si>
+    <t>692,465,101.3</t>
+  </si>
+  <si>
+    <t>534,560,879.98</t>
+  </si>
+  <si>
+    <t>408,483,504.8</t>
+  </si>
+  <si>
+    <t>396,132,567.5</t>
+  </si>
+  <si>
+    <t>383,916,339.75</t>
+  </si>
+  <si>
+    <t>370,864,468.98</t>
+  </si>
+  <si>
+    <t>510,017,637.4</t>
+  </si>
+  <si>
+    <t>425,960,683.0</t>
+  </si>
+  <si>
+    <t>208,644,229.58</t>
+  </si>
+  <si>
+    <t>238,285,025.0</t>
+  </si>
+  <si>
+    <t>204,248,546.8</t>
+  </si>
+  <si>
+    <t>203,886,610.4</t>
+  </si>
+  <si>
+    <t>161,322,285.9</t>
+  </si>
+  <si>
+    <t>578,447,604.29</t>
+  </si>
+  <si>
+    <t>266,504,418.3</t>
+  </si>
+  <si>
+    <t>325,916,650.39</t>
+  </si>
+  <si>
+    <t>170,198,479.8</t>
+  </si>
+  <si>
+    <t>191,884,020.7</t>
+  </si>
+  <si>
+    <t>180,029,729.35</t>
+  </si>
+  <si>
+    <t>209,542,183.08</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,325 +182,325 @@
     <t>NGPL</t>
   </si>
   <si>
-    <t>111,786,447.5</t>
+    <t>111,276,141.5</t>
   </si>
   <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>53,811,409.2</t>
+    <t>53,609,659.2</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>38,680,779.0</t>
+  </si>
+  <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>33,885,789.6</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>32,444,831.8</t>
+  </si>
+  <si>
+    <t>318,846,896.3</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>29,461,342.0</t>
+  </si>
+  <si>
+    <t>MBL</t>
+  </si>
+  <si>
+    <t>7,758,500.0</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>5,482,696.6</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>4,491,148.0</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>34,491,240.9</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>32,264,186.8</t>
+  </si>
+  <si>
+    <t>LBBL</t>
+  </si>
+  <si>
+    <t>7,509,467.8</t>
+  </si>
+  <si>
+    <t>7,011,691.4</t>
+  </si>
+  <si>
+    <t>4,223,460.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>26,988,208.0</t>
+  </si>
+  <si>
+    <t>BARUN</t>
+  </si>
+  <si>
+    <t>19,277,617.39</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>17,635,280.0</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>16,621,179.0</t>
+  </si>
+  <si>
+    <t>7,630,835.3</t>
+  </si>
+  <si>
+    <t>NMLBBL</t>
+  </si>
+  <si>
+    <t>43,572,040.0</t>
+  </si>
+  <si>
+    <t>UHEWA</t>
+  </si>
+  <si>
+    <t>8,991,325.0</t>
+  </si>
+  <si>
+    <t>4,957,797.0</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>4,771,077.5</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>4,764,793.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>14,476,839.6</t>
+  </si>
+  <si>
+    <t>11,896,656.0</t>
+  </si>
+  <si>
+    <t>MLBS</t>
+  </si>
+  <si>
+    <t>9,025,275.0</t>
+  </si>
+  <si>
+    <t>9,024,828.1</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>7,431,580.0</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>24,659,130.0</t>
+  </si>
+  <si>
+    <t>TSHL</t>
+  </si>
+  <si>
+    <t>12,163,330.0</t>
+  </si>
+  <si>
+    <t>10,820,176.8</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>9,097,780.0</t>
+  </si>
+  <si>
+    <t>5,751,756.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>117,234,083.7</t>
+  </si>
+  <si>
+    <t>45,017,019.8</t>
+  </si>
+  <si>
+    <t>37,877,417.0</t>
+  </si>
+  <si>
+    <t>HPPL</t>
+  </si>
+  <si>
+    <t>25,163,448.8</t>
+  </si>
+  <si>
+    <t>22,536,743.0</t>
+  </si>
+  <si>
+    <t>195,664,325.3</t>
+  </si>
+  <si>
+    <t>MEHL</t>
+  </si>
+  <si>
+    <t>7,462,297.0</t>
+  </si>
+  <si>
+    <t>4,768,181.0</t>
+  </si>
+  <si>
+    <t>3,289,500.0</t>
+  </si>
+  <si>
+    <t>USHL</t>
+  </si>
+  <si>
+    <t>2,899,090.0</t>
   </si>
   <si>
     <t>RHPL</t>
   </si>
   <si>
-    <t>44,647,256.5</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>39,279,793.0</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>36,313,259.79</t>
-  </si>
-  <si>
-    <t>318,856,096.3</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>29,461,342.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>5,757,468.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>2,552,625.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>2,499,448.5</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>61,843,006.4</t>
-  </si>
-  <si>
-    <t>GBLBS</t>
-  </si>
-  <si>
-    <t>34,096,392.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>32,816,186.8</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>30,508,878.0</t>
+    <t>53,689,877.0</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>29,619,559.2</t>
+  </si>
+  <si>
+    <t>28,276,712.8</t>
+  </si>
+  <si>
+    <t>15,006,254.4</t>
+  </si>
+  <si>
+    <t>JBLB</t>
+  </si>
+  <si>
+    <t>14,923,812.2</t>
+  </si>
+  <si>
+    <t>AVYAN</t>
+  </si>
+  <si>
+    <t>16,091,776.0</t>
+  </si>
+  <si>
+    <t>SJCL</t>
+  </si>
+  <si>
+    <t>10,278,662.3</t>
+  </si>
+  <si>
+    <t>10,098,191.3</t>
+  </si>
+  <si>
+    <t>8,387,377.2</t>
+  </si>
+  <si>
+    <t>4,908,345.8</t>
+  </si>
+  <si>
+    <t>29,790,885.0</t>
+  </si>
+  <si>
+    <t>18,032,013.5</t>
+  </si>
+  <si>
+    <t>14,456,424.0</t>
+  </si>
+  <si>
+    <t>12,185,279.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>7,235,512.0</t>
+  </si>
+  <si>
+    <t>TPC</t>
+  </si>
+  <si>
+    <t>16,780,146.89</t>
+  </si>
+  <si>
+    <t>13,101,790.0</t>
+  </si>
+  <si>
+    <t>7,364,932.0</t>
+  </si>
+  <si>
+    <t>6,465,727.2</t>
   </si>
   <si>
     <t>SHL</t>
   </si>
   <si>
-    <t>18,190,810.5</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>21,106,476.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>11,322,683.0</t>
-  </si>
-  <si>
-    <t>DORDI</t>
-  </si>
-  <si>
-    <t>10,767,906.5</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>9,692,593.4</t>
-  </si>
-  <si>
-    <t>9,074,828.1</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>34,068,229.1</t>
-  </si>
-  <si>
-    <t>SJCL</t>
-  </si>
-  <si>
-    <t>8,477,033.19</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>7,606,310.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>5,617,833.0</t>
-  </si>
-  <si>
-    <t>UHEWA</t>
-  </si>
-  <si>
-    <t>5,457,685.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>17,989,417.5</t>
-  </si>
-  <si>
-    <t>8,189,536.7</t>
-  </si>
-  <si>
-    <t>RHGCL</t>
-  </si>
-  <si>
-    <t>4,543,880.0</t>
-  </si>
-  <si>
-    <t>4,154,488.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>3,695,558.0</t>
-  </si>
-  <si>
-    <t>12,219,010.8</t>
-  </si>
-  <si>
-    <t>8,900,247.1</t>
-  </si>
-  <si>
-    <t>8,632,835.3</t>
-  </si>
-  <si>
-    <t>CKHL</t>
-  </si>
-  <si>
-    <t>6,458,060.0</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>4,643,824.59</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>117,234,083.7</t>
-  </si>
-  <si>
-    <t>45,017,019.8</t>
-  </si>
-  <si>
-    <t>37,969,417.0</t>
-  </si>
-  <si>
-    <t>25,457,884.4</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>20,169,672.5</t>
-  </si>
-  <si>
-    <t>195,756,145.3</t>
-  </si>
-  <si>
-    <t>27,234,296.0</t>
-  </si>
-  <si>
-    <t>11,647,694.0</t>
-  </si>
-  <si>
-    <t>8,130,000.0</t>
-  </si>
-  <si>
-    <t>4,569,005.0</t>
-  </si>
-  <si>
-    <t>28,276,712.8</t>
-  </si>
-  <si>
-    <t>15,006,254.4</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>14,779,540.0</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>8,821,779.19</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>7,975,500.4</t>
-  </si>
-  <si>
-    <t>HURJA</t>
-  </si>
-  <si>
-    <t>47,587,354.3</t>
-  </si>
-  <si>
-    <t>37,143,875.2</t>
-  </si>
-  <si>
-    <t>14,157,478.0</t>
-  </si>
-  <si>
-    <t>MHCL</t>
-  </si>
-  <si>
-    <t>10,102,446.0</t>
-  </si>
-  <si>
-    <t>MKHC</t>
-  </si>
-  <si>
-    <t>9,588,153.0</t>
-  </si>
-  <si>
-    <t>29,940,513.0</t>
-  </si>
-  <si>
-    <t>26,289,795.0</t>
-  </si>
-  <si>
-    <t>SMHL</t>
-  </si>
-  <si>
-    <t>21,615,210.0</t>
-  </si>
-  <si>
-    <t>18,912,945.0</t>
-  </si>
-  <si>
-    <t>18,626,709.8</t>
-  </si>
-  <si>
-    <t>64,273,597.0</t>
-  </si>
-  <si>
-    <t>26,973,520.0</t>
-  </si>
-  <si>
-    <t>17,433,198.5</t>
-  </si>
-  <si>
-    <t>11,811,417.0</t>
-  </si>
-  <si>
-    <t>5,846,886.2</t>
-  </si>
-  <si>
-    <t>31,602,375.0</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>17,660,704.7</t>
-  </si>
-  <si>
-    <t>17,049,451.0</t>
-  </si>
-  <si>
-    <t>13,818,480.5</t>
-  </si>
-  <si>
-    <t>12,353,690.0</t>
+    <t>6,193,847.6</t>
+  </si>
+  <si>
+    <t>63,708,786.8</t>
+  </si>
+  <si>
+    <t>17,007,982.5</t>
+  </si>
+  <si>
+    <t>12,360,995.0</t>
+  </si>
+  <si>
+    <t>8,990,545.29</t>
+  </si>
+  <si>
+    <t>7,493,608.6</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -518,109 +518,112 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>570,688,670.29</t>
-  </si>
-  <si>
-    <t>458,663,986.0</t>
-  </si>
-  <si>
-    <t>298,412,655.3</t>
-  </si>
-  <si>
-    <t>261,494,750.8</t>
-  </si>
-  <si>
-    <t>238,937,529.0</t>
+    <t>563,589,743.9</t>
+  </si>
+  <si>
+    <t>274,500,321.1</t>
+  </si>
+  <si>
+    <t>211,246,337.5</t>
+  </si>
+  <si>
+    <t>174,281,493.4</t>
+  </si>
+  <si>
+    <t>PHCL</t>
+  </si>
+  <si>
+    <t>153,942,628.5</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,340,028,275.69</t>
+    <t>2,064,506,473.2</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,569,393,478.6</t>
+    <t>1,313,765,925.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,395,408,057.58</t>
+    <t>1,287,092,199.08</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>555,951,062.5</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>613,856,895.0</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>460,203,849.9</t>
+    <t>454,864,626.7</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>408,945,448.3</t>
+    <t>445,984,678.5</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>405,740,156.1</t>
+    <t>406,648,700.7</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>104,917,742.0</t>
+    <t>111,977,151.0</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>79,262,894.4</t>
+    <t>107,852,110.1</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>73,270,094.5</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>59,073,603.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>79,146,087.4</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>76,163,417.3</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>41,925,719.9</t>
+    <t>47,173,907.4</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>12,132,513.78</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>12,994,181.0</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>12,036,754.28</t>
+    <t>4,162,404.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>547,242.1</t>
+    <t>463,967.1</t>
   </si>
   <si>
     <t>Total</t>
@@ -632,214 +635,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>204,327,157.5</t>
-  </si>
-  <si>
-    <t>108,577,812.8</t>
-  </si>
-  <si>
-    <t>50,847,134.5</t>
-  </si>
-  <si>
-    <t>45,323,813.5</t>
-  </si>
-  <si>
-    <t>44,488,355.4</t>
-  </si>
-  <si>
-    <t>366,019,959.8</t>
-  </si>
-  <si>
-    <t>20,218,958.1</t>
-  </si>
-  <si>
-    <t>14,975,457.1</t>
-  </si>
-  <si>
-    <t>8,035,604.7</t>
-  </si>
-  <si>
-    <t>4,694,260.9</t>
-  </si>
-  <si>
-    <t>80,976,661.3</t>
-  </si>
-  <si>
-    <t>75,859,904.8</t>
-  </si>
-  <si>
-    <t>68,973,318.88</t>
-  </si>
-  <si>
-    <t>48,490,034.2</t>
-  </si>
-  <si>
-    <t>26,707,018.5</t>
-  </si>
-  <si>
-    <t>64,656,250.5</t>
-  </si>
-  <si>
-    <t>43,766,922.6</t>
-  </si>
-  <si>
-    <t>38,034,652.1</t>
-  </si>
-  <si>
-    <t>29,911,934.3</t>
-  </si>
-  <si>
-    <t>22,112,128.1</t>
-  </si>
-  <si>
-    <t>68,042,835.5</t>
-  </si>
-  <si>
-    <t>55,060,123.0</t>
-  </si>
-  <si>
-    <t>29,125,199.2</t>
-  </si>
-  <si>
-    <t>19,427,662.6</t>
-  </si>
-  <si>
-    <t>13,634,837.7</t>
-  </si>
-  <si>
-    <t>68,527,947.0</t>
-  </si>
-  <si>
-    <t>29,382,053.5</t>
-  </si>
-  <si>
-    <t>21,309,438.89</t>
-  </si>
-  <si>
-    <t>18,148,350.0</t>
-  </si>
-  <si>
-    <t>15,038,012.9</t>
-  </si>
-  <si>
-    <t>76,119,950.59</t>
-  </si>
-  <si>
-    <t>42,593,605.2</t>
-  </si>
-  <si>
-    <t>22,882,045.4</t>
-  </si>
-  <si>
-    <t>14,260,382.5</t>
-  </si>
-  <si>
-    <t>9,116,134.5</t>
-  </si>
-  <si>
-    <t>249,832,167.2</t>
-  </si>
-  <si>
-    <t>102,198,055.3</t>
-  </si>
-  <si>
-    <t>60,403,967.1</t>
-  </si>
-  <si>
-    <t>52,523,860.7</t>
-  </si>
-  <si>
-    <t>32,265,151.2</t>
-  </si>
-  <si>
-    <t>214,968,232.2</t>
-  </si>
-  <si>
-    <t>42,213,914.4</t>
-  </si>
-  <si>
-    <t>21,138,751.7</t>
-  </si>
-  <si>
-    <t>12,718,059.4</t>
-  </si>
-  <si>
-    <t>5,408,407.8</t>
-  </si>
-  <si>
-    <t>99,749,165.4</t>
-  </si>
-  <si>
-    <t>50,560,274.1</t>
-  </si>
-  <si>
-    <t>41,288,817.9</t>
-  </si>
-  <si>
-    <t>23,611,913.0</t>
-  </si>
-  <si>
-    <t>16,906,650.6</t>
-  </si>
-  <si>
-    <t>89,249,835.0</t>
-  </si>
-  <si>
-    <t>46,877,681.0</t>
-  </si>
-  <si>
-    <t>46,227,726.4</t>
-  </si>
-  <si>
-    <t>42,295,022.0</t>
-  </si>
-  <si>
-    <t>15,893,538.9</t>
-  </si>
-  <si>
-    <t>75,551,081.7</t>
-  </si>
-  <si>
-    <t>63,251,376.2</t>
-  </si>
-  <si>
-    <t>53,302,971.3</t>
-  </si>
-  <si>
-    <t>31,181,849.8</t>
-  </si>
-  <si>
-    <t>8,619,663.69</t>
-  </si>
-  <si>
-    <t>79,016,170.09</t>
-  </si>
-  <si>
-    <t>65,855,059.3</t>
-  </si>
-  <si>
-    <t>62,863,106.0</t>
-  </si>
-  <si>
-    <t>28,094,069.4</t>
-  </si>
-  <si>
-    <t>17,326,523.39</t>
-  </si>
-  <si>
-    <t>72,930,508.0</t>
-  </si>
-  <si>
-    <t>57,378,164.1</t>
-  </si>
-  <si>
-    <t>40,815,357.0</t>
-  </si>
-  <si>
-    <t>33,397,222.3</t>
-  </si>
-  <si>
-    <t>13,490,916.4</t>
+    <t>171,814,512.8</t>
+  </si>
+  <si>
+    <t>95,876,871.8</t>
+  </si>
+  <si>
+    <t>57,524,022.8</t>
+  </si>
+  <si>
+    <t>43,010,971.9</t>
+  </si>
+  <si>
+    <t>42,546,675.9</t>
+  </si>
+  <si>
+    <t>363,756,677.8</t>
+  </si>
+  <si>
+    <t>22,083,975.8</t>
+  </si>
+  <si>
+    <t>14,334,369.5</t>
+  </si>
+  <si>
+    <t>11,110,956.5</t>
+  </si>
+  <si>
+    <t>5,235,250.7</t>
+  </si>
+  <si>
+    <t>70,807,057.8</t>
+  </si>
+  <si>
+    <t>49,663,875.4</t>
+  </si>
+  <si>
+    <t>26,203,264.58</t>
+  </si>
+  <si>
+    <t>22,183,459.1</t>
+  </si>
+  <si>
+    <t>15,608,962.2</t>
+  </si>
+  <si>
+    <t>80,170,075.59</t>
+  </si>
+  <si>
+    <t>76,838,364.1</t>
+  </si>
+  <si>
+    <t>25,211,772.4</t>
+  </si>
+  <si>
+    <t>19,579,408.39</t>
+  </si>
+  <si>
+    <t>19,093,480.5</t>
+  </si>
+  <si>
+    <t>78,207,481.59</t>
+  </si>
+  <si>
+    <t>51,759,903.2</t>
+  </si>
+  <si>
+    <t>22,203,504.0</t>
+  </si>
+  <si>
+    <t>15,813,947.6</t>
+  </si>
+  <si>
+    <t>11,806,156.7</t>
+  </si>
+  <si>
+    <t>46,762,830.1</t>
+  </si>
+  <si>
+    <t>37,787,555.6</t>
+  </si>
+  <si>
+    <t>32,504,476.0</t>
+  </si>
+  <si>
+    <t>30,603,248.2</t>
+  </si>
+  <si>
+    <t>24,676,694.3</t>
+  </si>
+  <si>
+    <t>64,835,766.2</t>
+  </si>
+  <si>
+    <t>29,151,202.2</t>
+  </si>
+  <si>
+    <t>28,929,703.8</t>
+  </si>
+  <si>
+    <t>12,388,510.2</t>
+  </si>
+  <si>
+    <t>10,353,107.0</t>
+  </si>
+  <si>
+    <t>264,217,689.6</t>
+  </si>
+  <si>
+    <t>88,587,054.9</t>
+  </si>
+  <si>
+    <t>62,126,231.9</t>
+  </si>
+  <si>
+    <t>61,161,876.7</t>
+  </si>
+  <si>
+    <t>32,689,725.5</t>
+  </si>
+  <si>
+    <t>207,129,080.2</t>
+  </si>
+  <si>
+    <t>21,765,386.2</t>
+  </si>
+  <si>
+    <t>18,777,237.6</t>
+  </si>
+  <si>
+    <t>6,473,810.7</t>
+  </si>
+  <si>
+    <t>3,919,118.5</t>
+  </si>
+  <si>
+    <t>138,748,996.3</t>
+  </si>
+  <si>
+    <t>43,670,328.5</t>
+  </si>
+  <si>
+    <t>43,091,729.5</t>
+  </si>
+  <si>
+    <t>35,081,345.7</t>
+  </si>
+  <si>
+    <t>34,886,899.1</t>
+  </si>
+  <si>
+    <t>66,054,309.6</t>
+  </si>
+  <si>
+    <t>26,521,537.7</t>
+  </si>
+  <si>
+    <t>25,802,045.1</t>
+  </si>
+  <si>
+    <t>24,201,127.9</t>
+  </si>
+  <si>
+    <t>9,659,398.3</t>
+  </si>
+  <si>
+    <t>59,353,220.7</t>
+  </si>
+  <si>
+    <t>32,696,616.4</t>
+  </si>
+  <si>
+    <t>31,595,127.6</t>
+  </si>
+  <si>
+    <t>20,176,966.8</t>
+  </si>
+  <si>
+    <t>19,444,859.7</t>
+  </si>
+  <si>
+    <t>56,020,852.1</t>
+  </si>
+  <si>
+    <t>38,637,097.0</t>
+  </si>
+  <si>
+    <t>29,811,194.9</t>
+  </si>
+  <si>
+    <t>13,888,597.1</t>
+  </si>
+  <si>
+    <t>12,917,752.4</t>
+  </si>
+  <si>
+    <t>114,726,853.98</t>
+  </si>
+  <si>
+    <t>35,438,867.1</t>
+  </si>
+  <si>
+    <t>29,276,925.9</t>
+  </si>
+  <si>
+    <t>6,799,318.0</t>
+  </si>
+  <si>
+    <t>6,748,064.9</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1651,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1014357175088128</v>
+        <v>0.1022321496699383</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>56</v>
@@ -1657,7 +1660,7 @@
         <v>64</v>
       </c>
       <c r="G9" s="12">
-        <v>0.4352693674695667</v>
+        <v>0.4604519357024817</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>73</v>
@@ -1666,43 +1669,43 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1008997949725907</v>
+        <v>0.06452256832054461</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.04219626994519591</v>
+        <v>0.0660692725235352</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07047192315978515</v>
+        <v>0.1099935818834184</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S9" s="16">
-        <v>0.03952462570891035</v>
+        <v>0.03770831845663844</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" s="18">
-        <v>0.02737654659447245</v>
+        <v>0.0664909476710475</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1714,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04882880728777366</v>
+        <v>0.04925252286078582</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>65</v>
@@ -1723,7 +1726,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04021757728940929</v>
+        <v>0.04254559824703184</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>75</v>
@@ -1732,43 +1735,43 @@
         <v>76</v>
       </c>
       <c r="J10" s="14">
-        <v>0.05562987898507276</v>
+        <v>0.06035643087314419</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02263641682163714</v>
+        <v>0.04719313552070756</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01753518888639115</v>
+        <v>0.02269776771131043</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01799326591852598</v>
+        <v>0.03098762612642876</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.0199408964787451</v>
+        <v>0.03279723731273902</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1780,7 +1783,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04051319814843838</v>
+        <v>0.03553699054237793</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
@@ -1789,7 +1792,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.007859499892479464</v>
+        <v>0.01120417474531868</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>77</v>
@@ -1798,43 +1801,43 @@
         <v>78</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05354116354702698</v>
+        <v>0.01404791873337412</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.02152730230373984</v>
+        <v>0.04317256337837806</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01573405216561449</v>
+        <v>0.01251549962500874</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.00998337807581616</v>
+        <v>0.02350844198472279</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0193417635601776</v>
+        <v>0.02917555523655061</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1846,7 +1849,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03564272839561022</v>
+        <v>0.03113171491546766</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
@@ -1855,52 +1858,52 @@
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.003484579664713792</v>
+        <v>0.007917650419793075</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.0497766799229182</v>
+        <v>0.013116731251008</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01937752600554561</v>
+        <v>0.04068996374318222</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01162078293938986</v>
+        <v>0.01204414353030946</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.009127843256301076</v>
+        <v>0.02350727792903219</v>
       </c>
       <c r="T12" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="U12" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="U12" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="V12" s="18">
-        <v>0.01446920568233713</v>
+        <v>0.02453127964785061</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1912,7 +1915,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03295087772510998</v>
+        <v>0.02980787126406225</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1921,52 +1924,52 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.003411988606277613</v>
+        <v>0.006485739124713345</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02967916918468649</v>
+        <v>0.007900802617950673</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>54</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01814248367249224</v>
+        <v>0.01868088970627144</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P13" s="18">
-        <v>0.011289508381001</v>
+        <v>0.01202827889176267</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="S13" s="16">
-        <v>0.00811952620119964</v>
+        <v>0.01935729019723235</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01040443310995824</v>
+        <v>0.0155090510984221</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1977,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1986,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1995,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2004,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2013,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2022,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2031,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2043,28 +2046,28 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1063789364681055</v>
+        <v>0.1077058588631641</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>56</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2672260450145002</v>
+        <v>0.2825620019444582</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.04613479664240305</v>
+        <v>0.1004373477573008</v>
       </c>
       <c r="K16" s="15" t="s">
         <v>137</v>
@@ -2073,34 +2076,34 @@
         <v>138</v>
       </c>
       <c r="M16" s="16">
-        <v>0.09513709669110462</v>
+        <v>0.03939394323371463</v>
       </c>
       <c r="N16" s="17" t="s">
         <v>73</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P16" s="18">
-        <v>0.06193352537659635</v>
+        <v>0.07520433169130937</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="R16" s="15" t="s">
         <v>151</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1412157933624223</v>
+        <v>0.04370782163355421</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V16" s="18">
-        <v>0.07080474073101656</v>
+        <v>0.1717845523870762</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2109,217 +2112,217 @@
         <v>65</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04084872366591156</v>
+        <v>0.04135825203723637</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03717744440503254</v>
+        <v>0.01077642322478151</v>
       </c>
       <c r="H17" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.05540914105257418</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.02516298009397612</v>
+      </c>
+      <c r="N17" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.02448341502793655</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.07425839276769214</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>62</v>
-      </c>
       <c r="O17" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P17" s="18">
-        <v>0.05438182324324289</v>
+        <v>0.04552014900920763</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="R17" s="15" t="s">
         <v>152</v>
       </c>
       <c r="S17" s="16">
-        <v>0.05926363552637585</v>
+        <v>0.03412667980876164</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="U17" s="17" t="s">
         <v>158</v>
       </c>
       <c r="V17" s="18">
-        <v>0.03956859626564603</v>
+        <v>0.04586037197571819</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03445368506577072</v>
+        <v>0.0347989219580791</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.006885806939654362</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.05289708592416628</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.02472117278014503</v>
+      </c>
+      <c r="N18" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="12">
-        <v>0.01590022727710057</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.02411351974294061</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.02830376626733768</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>147</v>
-      </c>
       <c r="O18" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P18" s="18">
-        <v>0.04471219838669629</v>
+        <v>0.03649390427864783</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="R18" s="15" t="s">
         <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.03830255457808111</v>
+        <v>0.01918368987575763</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="U18" s="17" t="s">
         <v>159</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03819908970959211</v>
+        <v>0.03333022177615674</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02310064259238948</v>
+        <v>0.02311828420051239</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01109823521830396</v>
+        <v>0.004750419903940942</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01439315072776709</v>
+        <v>0.0280721148179819</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>142</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02019690726783403</v>
+        <v>0.02053296424810738</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03912242115235872</v>
+        <v>0.0307606089469026</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="R19" s="15" t="s">
         <v>154</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02595091453166067</v>
+        <v>0.01684150042743785</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="U19" s="17" t="s">
         <v>160</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03096013920153495</v>
+        <v>0.02424213170036745</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01830208623415883</v>
+        <v>0.02070506446747109</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>128</v>
       </c>
       <c r="G20" s="12">
-        <v>0.006237133112374768</v>
+        <v>0.004186622538171802</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>135</v>
@@ -2328,43 +2331,43 @@
         <v>136</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01301240677011807</v>
+        <v>0.02791789066300242</v>
       </c>
       <c r="K20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L20" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>144</v>
-      </c>
       <c r="M20" s="16">
-        <v>0.0191687277527447</v>
+        <v>0.01201601960011385</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0385303285912568</v>
+        <v>0.01826538031362443</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01284621854029421</v>
+        <v>0.01613332634925966</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="U20" s="17" t="s">
         <v>161</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02767829372068878</v>
+        <v>0.02020578736110769</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2385,7 +2388,7 @@
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>168</v>
@@ -2393,7 +2396,7 @@
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>169</v>
@@ -2409,10 +2412,10 @@
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2428,178 +2431,178 @@
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3027649481324279</v>
+        <v>0.2671165138337818</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2030562365771243</v>
+        <v>0.1699818230241762</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1805451039049513</v>
+        <v>0.1665306385152706</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07942397658413398</v>
+        <v>0.07193182080316034</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05954355175628664</v>
+        <v>0.05885273547342276</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05291147492929501</v>
+        <v>0.05770380189680287</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05249675766422607</v>
+        <v>0.05261430985859548</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01357479952044558</v>
+        <v>0.01448818232950212</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01025544279146084</v>
+        <v>0.01395446322571947</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01024032969831417</v>
+        <v>0.009480063378428428</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D41" s="22">
-        <v>0.009854416430726619</v>
+        <v>0.007643248065091145</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D42" s="22">
-        <v>0.005424566251081305</v>
+        <v>0.006103603864740665</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001681254272584164</v>
+        <v>0.001569767315832468</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001557377456978299</v>
+        <v>0.0005385533346981557</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D45" s="22">
-        <v>7.080501023980892E-05</v>
+        <v>6.003046049716286E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -2978,331 +2981,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1854077331471571</v>
+        <v>0.1578502520959278</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G9" s="12">
-        <v>0.4996525963658743</v>
+        <v>0.5253068741184229</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1321172594664627</v>
+        <v>0.1324583605943053</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1292613982429946</v>
+        <v>0.1962627001040165</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1407501828420515</v>
+        <v>0.1974275482916461</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1505630438436957</v>
+        <v>0.1218047404037327</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1705458329220759</v>
+        <v>0.1748233428193318</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09852418243191378</v>
+        <v>0.0880844588571854</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G10" s="12">
-        <v>0.02760083061043445</v>
+        <v>0.03189182495773524</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1237690288122902</v>
+        <v>0.09290592944597464</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M10" s="16">
-        <v>0.08749925286912394</v>
+        <v>0.1881064062491857</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P10" s="18">
-        <v>0.113894759420422</v>
+        <v>0.1306630846503172</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0645554347241471</v>
+        <v>0.0984265364287611</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="V10" s="18">
-        <v>0.09543045967226448</v>
+        <v>0.07860338381882592</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" s="10">
-        <v>0.04613900599421595</v>
+        <v>0.05284874573501046</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0204429453133358</v>
+        <v>0.02070049374775618</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J11" s="14">
-        <v>0.112533237607464</v>
+        <v>0.04901829812346231</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07603924251889384</v>
+        <v>0.06172041735771945</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06024700591307917</v>
+        <v>0.05605069065673324</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="S11" s="16">
-        <v>0.04681905884887014</v>
+        <v>0.0846655185897177</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05126694724502035</v>
+        <v>0.07800613490843773</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04112711017682277</v>
+        <v>0.03951524610269051</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01096937651683995</v>
+        <v>0.01604551114437512</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J12" s="14">
-        <v>0.07911378818404129</v>
+        <v>0.04149847085860449</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M12" s="16">
-        <v>0.05980022692114802</v>
+        <v>0.04793194381150442</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P12" s="18">
-        <v>0.04018714157118991</v>
+        <v>0.03992084695232739</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="S12" s="16">
-        <v>0.03987381698069452</v>
+        <v>0.07971332561653492</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03195021531253982</v>
+        <v>0.03340441383902993</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D13" s="10">
-        <v>0.04036901030230935</v>
+        <v>0.03908868585784994</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G13" s="12">
-        <v>0.006408119513442463</v>
+        <v>0.007560309812251329</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J13" s="14">
-        <v>0.04357376602213805</v>
+        <v>0.02919959687395006</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M13" s="16">
-        <v>0.04420677930178168</v>
+        <v>0.04674235379308271</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0282043786857868</v>
+        <v>0.02980354979270923</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0330400821081764</v>
+        <v>0.0642762282951256</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02042458959940749</v>
+        <v>0.02791614691068807</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3313,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3322,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3331,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3340,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3349,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3358,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3367,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3376,331 +3379,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2266992618824717</v>
+        <v>0.242743341245639</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2934523991904775</v>
+        <v>0.2991184390536736</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1627454893193394</v>
+        <v>0.2595569587980159</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1784291290608718</v>
+        <v>0.1617061859874641</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1562813848812896</v>
+        <v>0.1498317118296516</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S16" s="16">
-        <v>0.173606763429338</v>
+        <v>0.1459194264471261</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1633999251740203</v>
+        <v>0.3093498126028002</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D17" s="10">
-        <v>0.09273515080941117</v>
+        <v>0.08138712336063383</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05762607029477841</v>
+        <v>0.03143174458776151</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08249148266582308</v>
+        <v>0.0816938353244889</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M17" s="16">
-        <v>0.09371831099994055</v>
+        <v>0.06492682663645222</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1308387973508451</v>
+        <v>0.08253958165153891</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1446904309086492</v>
+        <v>0.1006393659232109</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1285550858985194</v>
+        <v>0.09555746118647766</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05481093531635147</v>
+        <v>0.05707690932139391</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02885643771069159</v>
+        <v>0.02711651109167601</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J18" s="14">
-        <v>0.06736466260751889</v>
+        <v>0.08061145346365829</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M18" s="16">
-        <v>0.09241891550854152</v>
+        <v>0.06316545171789273</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P18" s="18">
-        <v>0.1102599987400529</v>
+        <v>0.07975897513147541</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1381167975866676</v>
+        <v>0.07765023733924052</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="V18" s="18">
-        <v>0.09144631598824082</v>
+        <v>0.07894238555804828</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D19" s="10">
-        <v>0.04766047777336722</v>
+        <v>0.05619093229332287</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01736137942700636</v>
+        <v>0.009348934246428284</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03852395475732642</v>
+        <v>0.06562647401604198</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M19" s="16">
-        <v>0.08455661502422289</v>
+        <v>0.05924627950851835</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P19" s="18">
-        <v>0.06450129581538953</v>
+        <v>0.05093488507480517</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S19" s="16">
-        <v>0.06172559937947694</v>
+        <v>0.03617610312977047</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="V19" s="18">
-        <v>0.07482607449875602</v>
+        <v>0.01833370022935973</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02927759881180883</v>
+        <v>0.03003286117703138</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G20" s="12">
-        <v>0.00738299900626197</v>
+        <v>0.00565966211530724</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02758400146622281</v>
+        <v>0.06526272386655989</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0317745159262433</v>
+        <v>0.02364697273327939</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01783022757498098</v>
+        <v>0.04908674846584029</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03806817826211865</v>
+        <v>0.03364731078758416</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03022623577898241</v>
+        <v>0.01819550122598536</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-11-24.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-11-24.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="263">
   <si>
     <t>Date: 2024-11-24</t>
   </si>
@@ -68,16 +68,16 @@
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
+    <t>Online Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
   </si>
   <si>
     <t>58</t>
@@ -89,79 +89,79 @@
     <t>45</t>
   </si>
   <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>1,088,465,241.69</t>
-  </si>
-  <si>
-    <t>692,465,101.3</t>
-  </si>
-  <si>
-    <t>534,560,879.98</t>
-  </si>
-  <si>
-    <t>408,483,504.8</t>
-  </si>
-  <si>
-    <t>396,132,567.5</t>
-  </si>
-  <si>
-    <t>383,916,339.75</t>
-  </si>
-  <si>
-    <t>370,864,468.98</t>
-  </si>
-  <si>
-    <t>510,017,637.4</t>
-  </si>
-  <si>
-    <t>425,960,683.0</t>
-  </si>
-  <si>
-    <t>208,644,229.58</t>
-  </si>
-  <si>
-    <t>238,285,025.0</t>
-  </si>
-  <si>
-    <t>204,248,546.8</t>
-  </si>
-  <si>
-    <t>203,886,610.4</t>
-  </si>
-  <si>
-    <t>161,322,285.9</t>
-  </si>
-  <si>
-    <t>578,447,604.29</t>
-  </si>
-  <si>
-    <t>266,504,418.3</t>
-  </si>
-  <si>
-    <t>325,916,650.39</t>
-  </si>
-  <si>
-    <t>170,198,479.8</t>
-  </si>
-  <si>
-    <t>191,884,020.7</t>
-  </si>
-  <si>
-    <t>180,029,729.35</t>
-  </si>
-  <si>
-    <t>209,542,183.08</t>
+    <t>57</t>
+  </si>
+  <si>
+    <t>1,259,744,918.9</t>
+  </si>
+  <si>
+    <t>765,210,394.4</t>
+  </si>
+  <si>
+    <t>561,910,688.28</t>
+  </si>
+  <si>
+    <t>472,087,132.5</t>
+  </si>
+  <si>
+    <t>460,251,112.91</t>
+  </si>
+  <si>
+    <t>438,599,219.38</t>
+  </si>
+  <si>
+    <t>397,475,437.25</t>
+  </si>
+  <si>
+    <t>657,727,222.79</t>
+  </si>
+  <si>
+    <t>451,650,611.5</t>
+  </si>
+  <si>
+    <t>272,258,423.68</t>
+  </si>
+  <si>
+    <t>242,103,776.1</t>
+  </si>
+  <si>
+    <t>226,109,083.04</t>
+  </si>
+  <si>
+    <t>219,843,390.88</t>
+  </si>
+  <si>
+    <t>189,345,862.35</t>
+  </si>
+  <si>
+    <t>602,017,696.1</t>
+  </si>
+  <si>
+    <t>313,559,782.89</t>
+  </si>
+  <si>
+    <t>289,652,264.6</t>
+  </si>
+  <si>
+    <t>229,983,356.4</t>
+  </si>
+  <si>
+    <t>234,142,029.87</t>
+  </si>
+  <si>
+    <t>218,755,828.5</t>
+  </si>
+  <si>
+    <t>208,129,574.9</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,325 +182,289 @@
     <t>NGPL</t>
   </si>
   <si>
-    <t>111,276,141.5</t>
+    <t>111,997,747.5</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>90,513,857.1</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>72,371,044.5</t>
   </si>
   <si>
     <t>JFL</t>
   </si>
   <si>
-    <t>53,609,659.2</t>
+    <t>55,400,435.8</t>
   </si>
   <si>
     <t>SBI</t>
   </si>
   <si>
-    <t>38,680,779.0</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>33,885,789.6</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>32,444,831.8</t>
-  </si>
-  <si>
-    <t>318,846,896.3</t>
+    <t>42,753,363.0</t>
+  </si>
+  <si>
+    <t>319,285,685.3</t>
   </si>
   <si>
     <t>MFIL</t>
   </si>
   <si>
-    <t>29,461,342.0</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
-    <t>7,758,500.0</t>
+    <t>29,468,932.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>6,059,678.0</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>3,822,054.0</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>2,845,393.0</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>34,161,070.79</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>11,837,929.4</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>10,648,249.0</t>
+  </si>
+  <si>
+    <t>9,046,503.0</t>
+  </si>
+  <si>
+    <t>8,960,961.9</t>
+  </si>
+  <si>
+    <t>SJCL</t>
+  </si>
+  <si>
+    <t>9,975,831.69</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>8,150,828.0</t>
   </si>
   <si>
     <t>CHCL</t>
   </si>
   <si>
-    <t>5,482,696.6</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>4,491,148.0</t>
-  </si>
-  <si>
-    <t>BFC</t>
-  </si>
-  <si>
-    <t>34,491,240.9</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>32,264,186.8</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>7,509,467.8</t>
-  </si>
-  <si>
-    <t>7,011,691.4</t>
-  </si>
-  <si>
-    <t>4,223,460.0</t>
+    <t>7,886,450.2</t>
+  </si>
+  <si>
+    <t>7,424,451.6</t>
+  </si>
+  <si>
+    <t>6,360,954.6</t>
+  </si>
+  <si>
+    <t>12,259,493.1</t>
+  </si>
+  <si>
+    <t>SLBSL</t>
+  </si>
+  <si>
+    <t>7,527,117.8</t>
+  </si>
+  <si>
+    <t>7,431,258.0</t>
+  </si>
+  <si>
+    <t>5,375,616.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>5,350,220.0</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>26,988,208.0</t>
-  </si>
-  <si>
-    <t>BARUN</t>
-  </si>
-  <si>
-    <t>19,277,617.39</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>17,635,280.0</t>
-  </si>
-  <si>
-    <t>CBBL</t>
-  </si>
-  <si>
-    <t>16,621,179.0</t>
-  </si>
-  <si>
-    <t>7,630,835.3</t>
-  </si>
-  <si>
-    <t>NMLBBL</t>
-  </si>
-  <si>
-    <t>43,572,040.0</t>
-  </si>
-  <si>
-    <t>UHEWA</t>
-  </si>
-  <si>
-    <t>8,991,325.0</t>
-  </si>
-  <si>
-    <t>4,957,797.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>4,771,077.5</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>4,764,793.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>14,476,839.6</t>
-  </si>
-  <si>
-    <t>11,896,656.0</t>
-  </si>
-  <si>
-    <t>MLBS</t>
-  </si>
-  <si>
-    <t>9,025,275.0</t>
-  </si>
-  <si>
-    <t>9,024,828.1</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>7,431,580.0</t>
-  </si>
-  <si>
-    <t>RFPL</t>
-  </si>
-  <si>
-    <t>24,659,130.0</t>
-  </si>
-  <si>
-    <t>TSHL</t>
-  </si>
-  <si>
-    <t>12,163,330.0</t>
-  </si>
-  <si>
-    <t>10,820,176.8</t>
-  </si>
-  <si>
-    <t>NMB</t>
-  </si>
-  <si>
-    <t>9,097,780.0</t>
-  </si>
-  <si>
-    <t>5,751,756.0</t>
+    <t>13,477,264.5</t>
+  </si>
+  <si>
+    <t>9,791,883.3</t>
+  </si>
+  <si>
+    <t>UMHL</t>
+  </si>
+  <si>
+    <t>6,768,295.6</t>
+  </si>
+  <si>
+    <t>6,030,967.0</t>
+  </si>
+  <si>
+    <t>5,803,661.0</t>
+  </si>
+  <si>
+    <t>7,914,213.2</t>
+  </si>
+  <si>
+    <t>5,250,462.2</t>
+  </si>
+  <si>
+    <t>4,749,048.0</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>4,651,917.09</t>
+  </si>
+  <si>
+    <t>4,410,877.59</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
-    <t>117,234,083.7</t>
-  </si>
-  <si>
-    <t>45,017,019.8</t>
-  </si>
-  <si>
-    <t>37,877,417.0</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>25,163,448.8</t>
-  </si>
-  <si>
-    <t>22,536,743.0</t>
-  </si>
-  <si>
-    <t>195,664,325.3</t>
-  </si>
-  <si>
-    <t>MEHL</t>
-  </si>
-  <si>
-    <t>7,462,297.0</t>
-  </si>
-  <si>
-    <t>4,768,181.0</t>
-  </si>
-  <si>
-    <t>3,289,500.0</t>
-  </si>
-  <si>
-    <t>USHL</t>
-  </si>
-  <si>
-    <t>2,899,090.0</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>53,689,877.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>29,619,559.2</t>
+    <t>123,899,874.2</t>
+  </si>
+  <si>
+    <t>45,030,537.8</t>
+  </si>
+  <si>
+    <t>37,969,417.0</t>
+  </si>
+  <si>
+    <t>26,490,326.1</t>
+  </si>
+  <si>
+    <t>21,778,045.2</t>
+  </si>
+  <si>
+    <t>196,962,978.4</t>
+  </si>
+  <si>
+    <t>20,201,892.7</t>
+  </si>
+  <si>
+    <t>5,938,945.0</t>
+  </si>
+  <si>
+    <t>3,261,276.0</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>2,582,606.0</t>
   </si>
   <si>
     <t>28,276,712.8</t>
   </si>
   <si>
-    <t>15,006,254.4</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>14,923,812.2</t>
+    <t>15,706,839.1</t>
+  </si>
+  <si>
+    <t>SARBTM</t>
+  </si>
+  <si>
+    <t>12,614,029.0</t>
+  </si>
+  <si>
+    <t>7,654,245.0</t>
+  </si>
+  <si>
+    <t>6,426,063.7</t>
+  </si>
+  <si>
+    <t>30,622,016.5</t>
+  </si>
+  <si>
+    <t>22,853,765.5</t>
+  </si>
+  <si>
+    <t>10,099,616.69</t>
+  </si>
+  <si>
+    <t>7,993,866.4</t>
+  </si>
+  <si>
+    <t>7,509,475.3</t>
+  </si>
+  <si>
+    <t>15,883,925.0</t>
+  </si>
+  <si>
+    <t>15,139,410.5</t>
+  </si>
+  <si>
+    <t>9,231,272.8</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>7,090,847.6</t>
+  </si>
+  <si>
+    <t>7,045,834.6</t>
+  </si>
+  <si>
+    <t>10,846,735.8</t>
+  </si>
+  <si>
+    <t>9,717,548.8</t>
+  </si>
+  <si>
+    <t>7,625,571.0</t>
   </si>
   <si>
     <t>AVYAN</t>
   </si>
   <si>
-    <t>16,091,776.0</t>
-  </si>
-  <si>
-    <t>SJCL</t>
-  </si>
-  <si>
-    <t>10,278,662.3</t>
-  </si>
-  <si>
-    <t>10,098,191.3</t>
-  </si>
-  <si>
-    <t>8,387,377.2</t>
-  </si>
-  <si>
-    <t>4,908,345.8</t>
-  </si>
-  <si>
-    <t>29,790,885.0</t>
-  </si>
-  <si>
-    <t>18,032,013.5</t>
-  </si>
-  <si>
-    <t>14,456,424.0</t>
-  </si>
-  <si>
-    <t>12,185,279.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>7,235,512.0</t>
-  </si>
-  <si>
-    <t>TPC</t>
-  </si>
-  <si>
-    <t>16,780,146.89</t>
-  </si>
-  <si>
-    <t>13,101,790.0</t>
-  </si>
-  <si>
-    <t>7,364,932.0</t>
-  </si>
-  <si>
-    <t>6,465,727.2</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>6,193,847.6</t>
-  </si>
-  <si>
-    <t>63,708,786.8</t>
-  </si>
-  <si>
-    <t>17,007,982.5</t>
-  </si>
-  <si>
-    <t>12,360,995.0</t>
-  </si>
-  <si>
-    <t>8,990,545.29</t>
-  </si>
-  <si>
-    <t>7,493,608.6</t>
+    <t>5,833,527.4</t>
+  </si>
+  <si>
+    <t>5,611,815.8</t>
+  </si>
+  <si>
+    <t>11,703,878.0</t>
+  </si>
+  <si>
+    <t>7,113,152.2</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>6,753,489.8</t>
+  </si>
+  <si>
+    <t>6,606,799.8</t>
+  </si>
+  <si>
+    <t>5,727,809.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -518,112 +482,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>563,589,743.9</t>
-  </si>
-  <si>
-    <t>274,500,321.1</t>
-  </si>
-  <si>
-    <t>211,246,337.5</t>
-  </si>
-  <si>
-    <t>174,281,493.4</t>
-  </si>
-  <si>
-    <t>PHCL</t>
-  </si>
-  <si>
-    <t>153,942,628.5</t>
+    <t>608,736,152.79</t>
+  </si>
+  <si>
+    <t>403,334,525.8</t>
+  </si>
+  <si>
+    <t>363,370,300.1</t>
+  </si>
+  <si>
+    <t>239,891,879.6</t>
+  </si>
+  <si>
+    <t>185,404,130.0</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>2,064,506,473.2</t>
+    <t>2,358,752,754.0</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>1,313,765,925.3</t>
+    <t>1,523,732,854.2</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,287,092,199.08</t>
+    <t>1,358,621,655.08</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>591,227,772.7</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>544,305,331.5</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>555,951,062.5</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>454,864,626.7</t>
+    <t>477,451,546.6</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>445,984,678.5</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>406,648,700.7</t>
+    <t>437,469,577.4</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>111,977,151.0</t>
+    <t>122,139,094.5</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>107,852,110.1</t>
+    <t>90,461,529.2</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>78,526,118.3</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>72,264,496.09</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>73,270,094.5</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>59,073,603.8</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>47,173,907.4</t>
+    <t>51,273,514.3</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>12,132,513.78</t>
+    <t>12,628,303.75</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>4,162,404.0</t>
+    <t>9,459,461.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>463,967.1</t>
+    <t>547,242.1</t>
   </si>
   <si>
     <t>Total</t>
@@ -635,214 +596,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>171,814,512.8</t>
-  </si>
-  <si>
-    <t>95,876,871.8</t>
-  </si>
-  <si>
-    <t>57,524,022.8</t>
-  </si>
-  <si>
-    <t>43,010,971.9</t>
-  </si>
-  <si>
-    <t>42,546,675.9</t>
-  </si>
-  <si>
-    <t>363,756,677.8</t>
-  </si>
-  <si>
-    <t>22,083,975.8</t>
-  </si>
-  <si>
-    <t>14,334,369.5</t>
-  </si>
-  <si>
-    <t>11,110,956.5</t>
-  </si>
-  <si>
-    <t>5,235,250.7</t>
-  </si>
-  <si>
-    <t>70,807,057.8</t>
-  </si>
-  <si>
-    <t>49,663,875.4</t>
-  </si>
-  <si>
-    <t>26,203,264.58</t>
-  </si>
-  <si>
-    <t>22,183,459.1</t>
-  </si>
-  <si>
-    <t>15,608,962.2</t>
-  </si>
-  <si>
-    <t>80,170,075.59</t>
-  </si>
-  <si>
-    <t>76,838,364.1</t>
-  </si>
-  <si>
-    <t>25,211,772.4</t>
-  </si>
-  <si>
-    <t>19,579,408.39</t>
-  </si>
-  <si>
-    <t>19,093,480.5</t>
-  </si>
-  <si>
-    <t>78,207,481.59</t>
-  </si>
-  <si>
-    <t>51,759,903.2</t>
-  </si>
-  <si>
-    <t>22,203,504.0</t>
-  </si>
-  <si>
-    <t>15,813,947.6</t>
-  </si>
-  <si>
-    <t>11,806,156.7</t>
-  </si>
-  <si>
-    <t>46,762,830.1</t>
-  </si>
-  <si>
-    <t>37,787,555.6</t>
-  </si>
-  <si>
-    <t>32,504,476.0</t>
-  </si>
-  <si>
-    <t>30,603,248.2</t>
-  </si>
-  <si>
-    <t>24,676,694.3</t>
-  </si>
-  <si>
-    <t>64,835,766.2</t>
-  </si>
-  <si>
-    <t>29,151,202.2</t>
-  </si>
-  <si>
-    <t>28,929,703.8</t>
-  </si>
-  <si>
-    <t>12,388,510.2</t>
-  </si>
-  <si>
-    <t>10,353,107.0</t>
-  </si>
-  <si>
-    <t>264,217,689.6</t>
-  </si>
-  <si>
-    <t>88,587,054.9</t>
-  </si>
-  <si>
-    <t>62,126,231.9</t>
-  </si>
-  <si>
-    <t>61,161,876.7</t>
-  </si>
-  <si>
-    <t>32,689,725.5</t>
-  </si>
-  <si>
-    <t>207,129,080.2</t>
-  </si>
-  <si>
-    <t>21,765,386.2</t>
-  </si>
-  <si>
-    <t>18,777,237.6</t>
-  </si>
-  <si>
-    <t>6,473,810.7</t>
-  </si>
-  <si>
-    <t>3,919,118.5</t>
-  </si>
-  <si>
-    <t>138,748,996.3</t>
-  </si>
-  <si>
-    <t>43,670,328.5</t>
-  </si>
-  <si>
-    <t>43,091,729.5</t>
-  </si>
-  <si>
-    <t>35,081,345.7</t>
-  </si>
-  <si>
-    <t>34,886,899.1</t>
-  </si>
-  <si>
-    <t>66,054,309.6</t>
-  </si>
-  <si>
-    <t>26,521,537.7</t>
-  </si>
-  <si>
-    <t>25,802,045.1</t>
-  </si>
-  <si>
-    <t>24,201,127.9</t>
-  </si>
-  <si>
-    <t>9,659,398.3</t>
-  </si>
-  <si>
-    <t>59,353,220.7</t>
-  </si>
-  <si>
-    <t>32,696,616.4</t>
-  </si>
-  <si>
-    <t>31,595,127.6</t>
-  </si>
-  <si>
-    <t>20,176,966.8</t>
-  </si>
-  <si>
-    <t>19,444,859.7</t>
-  </si>
-  <si>
-    <t>56,020,852.1</t>
-  </si>
-  <si>
-    <t>38,637,097.0</t>
-  </si>
-  <si>
-    <t>29,811,194.9</t>
-  </si>
-  <si>
-    <t>13,888,597.1</t>
-  </si>
-  <si>
-    <t>12,917,752.4</t>
-  </si>
-  <si>
-    <t>114,726,853.98</t>
-  </si>
-  <si>
-    <t>35,438,867.1</t>
-  </si>
-  <si>
-    <t>29,276,925.9</t>
-  </si>
-  <si>
-    <t>6,799,318.0</t>
-  </si>
-  <si>
-    <t>6,748,064.9</t>
+    <t>241,896,208.8</t>
+  </si>
+  <si>
+    <t>106,693,319.0</t>
+  </si>
+  <si>
+    <t>97,356,727.8</t>
+  </si>
+  <si>
+    <t>70,055,344.09</t>
+  </si>
+  <si>
+    <t>52,491,896.7</t>
+  </si>
+  <si>
+    <t>368,345,135.6</t>
+  </si>
+  <si>
+    <t>32,207,398.3</t>
+  </si>
+  <si>
+    <t>20,775,782.2</t>
+  </si>
+  <si>
+    <t>9,204,007.69</t>
+  </si>
+  <si>
+    <t>6,690,777.4</t>
+  </si>
+  <si>
+    <t>97,315,328.0</t>
+  </si>
+  <si>
+    <t>46,092,920.68</t>
+  </si>
+  <si>
+    <t>39,176,440.5</t>
+  </si>
+  <si>
+    <t>23,199,453.5</t>
+  </si>
+  <si>
+    <t>20,444,696.39</t>
+  </si>
+  <si>
+    <t>78,453,913.3</t>
+  </si>
+  <si>
+    <t>46,910,624.9</t>
+  </si>
+  <si>
+    <t>33,497,013.5</t>
+  </si>
+  <si>
+    <t>28,497,324.6</t>
+  </si>
+  <si>
+    <t>16,386,035.7</t>
+  </si>
+  <si>
+    <t>70,647,483.09</t>
+  </si>
+  <si>
+    <t>42,070,230.1</t>
+  </si>
+  <si>
+    <t>39,564,139.79</t>
+  </si>
+  <si>
+    <t>24,877,359.0</t>
+  </si>
+  <si>
+    <t>15,055,408.3</t>
+  </si>
+  <si>
+    <t>84,380,326.59</t>
+  </si>
+  <si>
+    <t>49,852,734.9</t>
+  </si>
+  <si>
+    <t>28,332,666.9</t>
+  </si>
+  <si>
+    <t>18,407,878.0</t>
+  </si>
+  <si>
+    <t>11,690,207.6</t>
+  </si>
+  <si>
+    <t>61,715,586.3</t>
+  </si>
+  <si>
+    <t>35,883,484.9</t>
+  </si>
+  <si>
+    <t>31,950,020.1</t>
+  </si>
+  <si>
+    <t>18,793,890.39</t>
+  </si>
+  <si>
+    <t>13,340,779.5</t>
+  </si>
+  <si>
+    <t>244,368,471.2</t>
+  </si>
+  <si>
+    <t>107,528,496.1</t>
+  </si>
+  <si>
+    <t>84,452,427.4</t>
+  </si>
+  <si>
+    <t>52,331,002.0</t>
+  </si>
+  <si>
+    <t>33,183,664.1</t>
+  </si>
+  <si>
+    <t>228,935,033.0</t>
+  </si>
+  <si>
+    <t>31,323,005.9</t>
+  </si>
+  <si>
+    <t>19,419,188.3</t>
+  </si>
+  <si>
+    <t>7,388,062.5</t>
+  </si>
+  <si>
+    <t>6,599,111.2</t>
+  </si>
+  <si>
+    <t>95,826,374.9</t>
+  </si>
+  <si>
+    <t>58,992,978.1</t>
+  </si>
+  <si>
+    <t>43,144,244.8</t>
+  </si>
+  <si>
+    <t>22,686,838.6</t>
+  </si>
+  <si>
+    <t>21,442,058.3</t>
+  </si>
+  <si>
+    <t>68,180,468.8</t>
+  </si>
+  <si>
+    <t>62,691,090.8</t>
+  </si>
+  <si>
+    <t>34,544,528.7</t>
+  </si>
+  <si>
+    <t>15,127,972.4</t>
+  </si>
+  <si>
+    <t>12,161,605.8</t>
+  </si>
+  <si>
+    <t>59,618,928.0</t>
+  </si>
+  <si>
+    <t>51,212,822.8</t>
+  </si>
+  <si>
+    <t>40,207,938.0</t>
+  </si>
+  <si>
+    <t>20,589,633.8</t>
+  </si>
+  <si>
+    <t>18,767,420.39</t>
+  </si>
+  <si>
+    <t>67,728,973.09</t>
+  </si>
+  <si>
+    <t>45,508,128.0</t>
+  </si>
+  <si>
+    <t>35,359,070.2</t>
+  </si>
+  <si>
+    <t>19,294,853.3</t>
+  </si>
+  <si>
+    <t>15,678,963.5</t>
+  </si>
+  <si>
+    <t>62,878,872.0</t>
+  </si>
+  <si>
+    <t>41,920,098.6</t>
+  </si>
+  <si>
+    <t>35,185,638.4</t>
+  </si>
+  <si>
+    <t>22,686,584.6</t>
+  </si>
+  <si>
+    <t>16,498,990.6</t>
   </si>
 </sst>
 </file>
@@ -1651,16 +1612,16 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1022321496699383</v>
+        <v>0.08890509961159089</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G9" s="12">
-        <v>0.4604519357024817</v>
+        <v>0.417252153965252</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>73</v>
@@ -1669,7 +1630,7 @@
         <v>74</v>
       </c>
       <c r="J9" s="14">
-        <v>0.06452256832054461</v>
+        <v>0.06079448480427826</v>
       </c>
       <c r="K9" s="15" t="s">
         <v>81</v>
@@ -1678,34 +1639,34 @@
         <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0660692725235352</v>
+        <v>0.02113133574976225</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1099935818834184</v>
+        <v>0.02663653113729089</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S9" s="16">
-        <v>0.03770831845663844</v>
+        <v>0.03072797192628693</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="V9" s="18">
-        <v>0.0664909476710475</v>
+        <v>0.01991120068891754</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1717,7 +1678,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04925252286078582</v>
+        <v>0.07185094041025068</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>65</v>
@@ -1726,7 +1687,7 @@
         <v>66</v>
       </c>
       <c r="G10" s="12">
-        <v>0.04254559824703184</v>
+        <v>0.0385108882676725</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>75</v>
@@ -1735,7 +1696,7 @@
         <v>76</v>
       </c>
       <c r="J10" s="14">
-        <v>0.06035643087314419</v>
+        <v>0.02106727927926718</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>83</v>
@@ -1744,34 +1705,34 @@
         <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.04719313552070756</v>
+        <v>0.01726551612799995</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02269776771131043</v>
+        <v>0.01635437175243049</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="S10" s="16">
-        <v>0.03098762612642876</v>
+        <v>0.02232535505613011</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03279723731273902</v>
+        <v>0.01320952619443908</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1783,7 +1744,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03553699054237793</v>
+        <v>0.05744896717916025</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>67</v>
@@ -1792,7 +1753,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01120417474531868</v>
+        <v>0.007918969794903769</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>77</v>
@@ -1801,7 +1762,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01404791873337412</v>
+        <v>0.01895007377879593</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>85</v>
@@ -1810,34 +1771,34 @@
         <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04317256337837806</v>
+        <v>0.01670549705143679</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01251549962500874</v>
+        <v>0.0161460945808797</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02350844198472279</v>
+        <v>0.01543161798045971</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02917555523655061</v>
+        <v>0.01194802887156268</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1849,7 +1810,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03113171491546766</v>
+        <v>0.04397750288080165</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>69</v>
@@ -1858,7 +1819,7 @@
         <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.007917650419793075</v>
+        <v>0.004994775329727278</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>60</v>
@@ -1867,43 +1828,43 @@
         <v>79</v>
       </c>
       <c r="J12" s="14">
-        <v>0.013116731251008</v>
+        <v>0.01609953892795883</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="M12" s="16">
-        <v>0.04068996374318222</v>
+        <v>0.01572686711599791</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01204414353030946</v>
+        <v>0.01167974579357764</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02350727792903219</v>
+        <v>0.0137505192292073</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02453127964785061</v>
+        <v>0.01170365930580532</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1915,7 +1876,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.02980787126406225</v>
+        <v>0.03393811108786366</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>71</v>
@@ -1924,52 +1885,52 @@
         <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.006485739124713345</v>
+        <v>0.003718445307098928</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.007900802617950673</v>
+        <v>0.01594730637252936</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01868088970627144</v>
+        <v>0.01347411137074362</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01202827889176267</v>
+        <v>0.01162456721977815</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01935729019723235</v>
+        <v>0.01323226477284662</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="V13" s="18">
-        <v>0.0155090510984221</v>
+        <v>0.01109723315361923</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1980,7 +1941,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1989,7 +1950,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1998,7 +1959,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2007,7 +1968,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2016,7 +1977,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2025,7 +1986,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2034,7 +1995,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2046,64 +2007,64 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1077058588631641</v>
+        <v>0.09835314462565045</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.257397154875867</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.05032243270999985</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.06486517931094002</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.03451143203016226</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.02473040379627864</v>
+      </c>
+      <c r="T16" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.2825620019444582</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.1004373477573008</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.03939394323371463</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="O16" s="17" t="s">
+      <c r="U16" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.07520433169130937</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.04370782163355421</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.1717845523870762</v>
+        <v>0.0294455377695166</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2112,497 +2073,497 @@
         <v>65</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04135825203723637</v>
+        <v>0.03574575862494474</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01077642322478151</v>
+        <v>0.02640044208474228</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>131</v>
+        <v>60</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>0.05540914105257418</v>
+        <v>0.0279525544318767</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02516298009397612</v>
+        <v>0.0484100580733367</v>
       </c>
       <c r="N17" s="17" t="s">
         <v>56</v>
       </c>
       <c r="O17" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.03289380530614913</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="R17" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.02215587345033728</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="P17" s="18">
-        <v>0.04552014900920763</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="S17" s="16">
-        <v>0.03412667980876164</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>158</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.04586037197571819</v>
+        <v>0.01789582835410794</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D18" s="10">
-        <v>0.0347989219580791</v>
+        <v>0.0301405597516953</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12">
-        <v>0.006885806939654362</v>
+        <v>0.007761192272690853</v>
       </c>
       <c r="H18" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0.02244845891543966</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.0213935437013844</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.02005703525980422</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="J18" s="14">
-        <v>0.05289708592416628</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.02472117278014503</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="O18" s="17" t="s">
+      <c r="R18" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.01738619373463418</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="P18" s="18">
-        <v>0.03649390427864783</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.01918368987575763</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>123</v>
-      </c>
       <c r="U18" s="17" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03333022177615674</v>
+        <v>0.01699096137040604</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02311828420051239</v>
+        <v>0.02102832541934851</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="G19" s="12">
-        <v>0.004750419903940942</v>
+        <v>0.004261933742493344</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>56</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0280721148179819</v>
+        <v>0.01362181777219709</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02053296424810738</v>
+        <v>0.01693303174282133</v>
       </c>
       <c r="N19" s="17" t="s">
         <v>135</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="P19" s="18">
-        <v>0.0307606089469026</v>
+        <v>0.01540647572836306</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01684150042743785</v>
+        <v>0.01330035974128322</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02424213170036745</v>
+        <v>0.01662190711886562</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02070506446747109</v>
+        <v>0.01728766266349891</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G20" s="12">
-        <v>0.004186622538171802</v>
+        <v>0.003375027337448828</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02791789066300242</v>
+        <v>0.01143609444353173</v>
       </c>
       <c r="K20" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01590696882635326</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.01530867476984848</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="R20" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.01201601960011385</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="O20" s="17" t="s">
+      <c r="S20" s="16">
+        <v>0.01279486043758312</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.01826538031362443</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01613332634925966</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>161</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.02020578736110769</v>
+        <v>0.0144104728574646</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2671165138337818</v>
+        <v>0.3051876178754294</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1699818230241762</v>
+        <v>0.1971484290853432</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1665306385152706</v>
+        <v>0.1757854890915109</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07193182080316034</v>
+        <v>0.07649610382695872</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05885273547342276</v>
+        <v>0.07042503595838129</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05770380189680287</v>
+        <v>0.06177514786604614</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="D37" s="22">
-        <v>0.05261430985859548</v>
+        <v>0.05660207412297387</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01448818232950212</v>
+        <v>0.01580298708150102</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01395446322571947</v>
+        <v>0.01170438001994871</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D40" s="22">
-        <v>0.009480063378428428</v>
+        <v>0.01016011489306825</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="D41" s="22">
-        <v>0.007643248065091145</v>
+        <v>0.009349953861983812</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D42" s="22">
-        <v>0.006103603864740665</v>
+        <v>0.006634032186197825</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="D43" s="22">
-        <v>0.001569767315832468</v>
+        <v>0.00163391518366399</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0005385533346981557</v>
+        <v>0.001223913936753172</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D45" s="22">
-        <v>6.003046049716286E-05</v>
+        <v>7.080501023980892E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2981,331 +2942,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1578502520959278</v>
+        <v>0.1920199916434051</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="G9" s="12">
-        <v>0.5253068741184229</v>
+        <v>0.4813645218303899</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1324583605943053</v>
+        <v>0.173186469006099</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1962627001040165</v>
+        <v>0.1661852397555021</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1974275482916461</v>
+        <v>0.15349769097422</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1218047404037327</v>
+        <v>0.1923859479715429</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1748233428193318</v>
+        <v>0.1552689311495311</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0880844588571854</v>
+        <v>0.08469438328289811</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03189182495773524</v>
+        <v>0.04208959854139692</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="J10" s="14">
-        <v>0.09290592944597464</v>
+        <v>0.08202890893762801</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1881064062491857</v>
+        <v>0.0993685734486737</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1306630846503172</v>
+        <v>0.09140712302465773</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0984265364287611</v>
+        <v>0.1136635285636654</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="V10" s="18">
-        <v>0.07860338381882592</v>
+        <v>0.09027849657394144</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05284874573501046</v>
+        <v>0.07728288984488317</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02070049374775618</v>
+        <v>0.02715041817523957</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04901829812346231</v>
+        <v>0.06972004860757941</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06172041735771945</v>
+        <v>0.07095515042448229</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05605069065673324</v>
+        <v>0.08596207307321946</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="S11" s="16">
-        <v>0.0846655185897177</v>
+        <v>0.06459807871990927</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07800613490843773</v>
+        <v>0.0803823761313442</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="D12" s="10">
-        <v>0.03951524610269051</v>
+        <v>0.05561073757786759</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01604551114437512</v>
+        <v>0.01202807458884147</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04149847085860449</v>
+        <v>0.04128672755987819</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04793194381150442</v>
+        <v>0.06036454425073744</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03992084695232739</v>
+        <v>0.05405170851779049</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="S12" s="16">
-        <v>0.07971332561653492</v>
+        <v>0.04196970078063799</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="V12" s="18">
-        <v>0.03340441383902993</v>
+        <v>0.04728314919288764</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03908868585784994</v>
+        <v>0.04166867110354018</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="G13" s="12">
-        <v>0.007560309812251329</v>
+        <v>0.008743709506515821</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02919959687395006</v>
+        <v>0.03638424544402404</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="M13" s="16">
-        <v>0.04674235379308271</v>
+        <v>0.03470976981140234</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02980354979270923</v>
+        <v>0.03271129146176344</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="S13" s="16">
-        <v>0.0642762282951256</v>
+        <v>0.0266535075382149</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02791614691068807</v>
+        <v>0.0335637834435768</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3316,7 +3277,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3325,7 +3286,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3334,7 +3295,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3343,7 +3304,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3352,7 +3313,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3361,7 +3322,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3370,7 +3331,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3379,331 +3340,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D16" s="10">
-        <v>0.242743341245639</v>
+        <v>0.1939825019603022</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2991184390536736</v>
+        <v>0.2991791991789494</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2595569587980159</v>
+        <v>0.1705366651652829</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1617061859874641</v>
+        <v>0.1444234847896431</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1498317118296516</v>
+        <v>0.1295356520119012</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1459194264471261</v>
+        <v>0.1544210981399855</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3093498126028002</v>
+        <v>0.1581956169041236</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D17" s="10">
-        <v>0.08138712336063383</v>
+        <v>0.08535735646696881</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03143174458776151</v>
+        <v>0.04093384790539902</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="J17" s="14">
-        <v>0.0816938353244889</v>
+        <v>0.1049863961131912</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="M17" s="16">
-        <v>0.06492682663645222</v>
+        <v>0.1327955931948643</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08253958165153891</v>
+        <v>0.1112714806406442</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1006393659232109</v>
+        <v>0.1037578864466058</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09555746118647766</v>
+        <v>0.1054658846092005</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05707690932139391</v>
+        <v>0.06703930782570112</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02711651109167601</v>
+        <v>0.02537758039111132</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08061145346365829</v>
+        <v>0.07678132076836601</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="M18" s="16">
-        <v>0.06316545171789273</v>
+        <v>0.07317405267342253</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07975897513147541</v>
+        <v>0.08736087077721522</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="S18" s="16">
-        <v>0.07765023733924052</v>
+        <v>0.08061817859590191</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07894238555804828</v>
+        <v>0.08852279940475744</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05619093229332287</v>
+        <v>0.04154095104086234</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="G19" s="12">
-        <v>0.009348934246428284</v>
+        <v>0.009654942685132976</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="J19" s="14">
-        <v>0.06562647401604198</v>
+        <v>0.04037445642730888</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05924627950851835</v>
+        <v>0.03204487341115996</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="P19" s="18">
-        <v>0.05093488507480517</v>
+        <v>0.04473565239162433</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03617610312977047</v>
+        <v>0.04399199188561036</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01833370022935973</v>
+        <v>0.05707669574995858</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03003286117703138</v>
+        <v>0.02634157407753288</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="G20" s="12">
-        <v>0.00565966211530724</v>
+        <v>0.008623917354356315</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="J20" s="14">
-        <v>0.06526272386655989</v>
+        <v>0.03815919281698274</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02364697273327939</v>
+        <v>0.02576135836534371</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04908674846584029</v>
+        <v>0.04077648021607257</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03364731078758416</v>
+        <v>0.0357478144219309</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01819550122598536</v>
+        <v>0.04150945958862518</v>
       </c>
     </row>
   </sheetData>
